--- a/artfynd/A 30810-2024 artfynd.xlsx
+++ b/artfynd/A 30810-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120026703</v>
+        <v>120026701</v>
       </c>
       <c r="B2" t="n">
-        <v>90562</v>
+        <v>57310</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>579662</v>
+        <v>579689</v>
       </c>
       <c r="R2" t="n">
-        <v>7194870</v>
+        <v>7194652</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,7 +777,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120026702</v>
+        <v>120026705</v>
       </c>
       <c r="B3" t="n">
         <v>90558</v>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>579658</v>
+        <v>579656</v>
       </c>
       <c r="R3" t="n">
-        <v>7194877</v>
+        <v>7194865</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -872,17 +872,17 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Maja Östlund, Per-Anders Blomqvist</t>
+          <t>Maja Östlund, Simon Mattsson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120026705</v>
+        <v>120026703</v>
       </c>
       <c r="B4" t="n">
-        <v>90558</v>
+        <v>90562</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1108</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>579656</v>
+        <v>579662</v>
       </c>
       <c r="R4" t="n">
-        <v>7194865</v>
+        <v>7194870</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120026701</v>
+        <v>120026702</v>
       </c>
       <c r="B5" t="n">
-        <v>57310</v>
+        <v>90558</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -997,21 +997,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>579689</v>
+        <v>579658</v>
       </c>
       <c r="R5" t="n">
-        <v>7194652</v>
+        <v>7194877</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1076,7 +1076,7 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Maja Östlund, Simon Mattsson</t>
+          <t>Maja Östlund, Per-Anders Blomqvist</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>

--- a/artfynd/A 30810-2024 artfynd.xlsx
+++ b/artfynd/A 30810-2024 artfynd.xlsx
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120026703</v>
+        <v>120026702</v>
       </c>
       <c r="B4" t="n">
-        <v>90562</v>
+        <v>90558</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>1108</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>579662</v>
+        <v>579658</v>
       </c>
       <c r="R4" t="n">
-        <v>7194870</v>
+        <v>7194877</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -974,17 +974,17 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Maja Östlund, Simon Mattsson</t>
+          <t>Maja Östlund, Per-Anders Blomqvist</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120026702</v>
+        <v>120026703</v>
       </c>
       <c r="B5" t="n">
-        <v>90558</v>
+        <v>90562</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -997,21 +997,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1108</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>579658</v>
+        <v>579662</v>
       </c>
       <c r="R5" t="n">
-        <v>7194877</v>
+        <v>7194870</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1076,7 +1076,7 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Maja Östlund, Per-Anders Blomqvist</t>
+          <t>Maja Östlund, Simon Mattsson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>

--- a/artfynd/A 30810-2024 artfynd.xlsx
+++ b/artfynd/A 30810-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120026701</v>
+        <v>120026705</v>
       </c>
       <c r="B2" t="n">
-        <v>57310</v>
+        <v>90558</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>579689</v>
+        <v>579656</v>
       </c>
       <c r="R2" t="n">
-        <v>7194652</v>
+        <v>7194865</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,7 +777,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120026705</v>
+        <v>120026702</v>
       </c>
       <c r="B3" t="n">
         <v>90558</v>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>579656</v>
+        <v>579658</v>
       </c>
       <c r="R3" t="n">
-        <v>7194865</v>
+        <v>7194877</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -872,17 +872,17 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Maja Östlund, Simon Mattsson</t>
+          <t>Maja Östlund, Per-Anders Blomqvist</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120026702</v>
+        <v>120026703</v>
       </c>
       <c r="B4" t="n">
-        <v>90558</v>
+        <v>90562</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1108</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>579658</v>
+        <v>579662</v>
       </c>
       <c r="R4" t="n">
-        <v>7194877</v>
+        <v>7194870</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -974,17 +974,17 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Maja Östlund, Per-Anders Blomqvist</t>
+          <t>Maja Östlund, Simon Mattsson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120026703</v>
+        <v>120026701</v>
       </c>
       <c r="B5" t="n">
-        <v>90562</v>
+        <v>57310</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -997,21 +997,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>579662</v>
+        <v>579689</v>
       </c>
       <c r="R5" t="n">
-        <v>7194870</v>
+        <v>7194652</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>

--- a/artfynd/A 30810-2024 artfynd.xlsx
+++ b/artfynd/A 30810-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120026705</v>
+        <v>120026703</v>
       </c>
       <c r="B2" t="n">
-        <v>90558</v>
+        <v>90580</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1108</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>579656</v>
+        <v>579662</v>
       </c>
       <c r="R2" t="n">
-        <v>7194865</v>
+        <v>7194870</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120026702</v>
+        <v>120026701</v>
       </c>
       <c r="B3" t="n">
-        <v>90558</v>
+        <v>57320</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>579658</v>
+        <v>579689</v>
       </c>
       <c r="R3" t="n">
-        <v>7194877</v>
+        <v>7194652</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -872,17 +872,17 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Maja Östlund, Per-Anders Blomqvist</t>
+          <t>Maja Östlund, Simon Mattsson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120026703</v>
+        <v>120026705</v>
       </c>
       <c r="B4" t="n">
-        <v>90562</v>
+        <v>90576</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>1108</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>579662</v>
+        <v>579656</v>
       </c>
       <c r="R4" t="n">
-        <v>7194870</v>
+        <v>7194865</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120026701</v>
+        <v>120026702</v>
       </c>
       <c r="B5" t="n">
-        <v>57310</v>
+        <v>90576</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -997,21 +997,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>579689</v>
+        <v>579658</v>
       </c>
       <c r="R5" t="n">
-        <v>7194652</v>
+        <v>7194877</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1076,7 +1076,7 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Maja Östlund, Simon Mattsson</t>
+          <t>Maja Östlund, Per-Anders Blomqvist</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>

--- a/artfynd/A 30810-2024 artfynd.xlsx
+++ b/artfynd/A 30810-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120026703</v>
+        <v>120026701</v>
       </c>
       <c r="B2" t="n">
-        <v>90580</v>
+        <v>57320</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>579662</v>
+        <v>579689</v>
       </c>
       <c r="R2" t="n">
-        <v>7194870</v>
+        <v>7194652</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -770,17 +770,17 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Maja Östlund, Simon Mattsson</t>
+          <t>Simon Mattsson, Maja Östlund</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120026701</v>
+        <v>120026705</v>
       </c>
       <c r="B3" t="n">
-        <v>57320</v>
+        <v>90576</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>579689</v>
+        <v>579656</v>
       </c>
       <c r="R3" t="n">
-        <v>7194652</v>
+        <v>7194865</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,7 +879,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120026705</v>
+        <v>120026702</v>
       </c>
       <c r="B4" t="n">
         <v>90576</v>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>579656</v>
+        <v>579658</v>
       </c>
       <c r="R4" t="n">
-        <v>7194865</v>
+        <v>7194877</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -974,17 +974,17 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Maja Östlund, Simon Mattsson</t>
+          <t>Maja Östlund, Per-Anders Blomqvist</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120026702</v>
+        <v>120026703</v>
       </c>
       <c r="B5" t="n">
-        <v>90576</v>
+        <v>90580</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -997,21 +997,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1108</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>579658</v>
+        <v>579662</v>
       </c>
       <c r="R5" t="n">
-        <v>7194877</v>
+        <v>7194870</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1076,7 +1076,7 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Maja Östlund, Per-Anders Blomqvist</t>
+          <t>Maja Östlund, Simon Mattsson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>

--- a/artfynd/A 30810-2024 artfynd.xlsx
+++ b/artfynd/A 30810-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120026701</v>
+        <v>120026702</v>
       </c>
       <c r="B2" t="n">
-        <v>57320</v>
+        <v>90576</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>579689</v>
+        <v>579658</v>
       </c>
       <c r="R2" t="n">
-        <v>7194652</v>
+        <v>7194877</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -770,17 +770,17 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Simon Mattsson, Maja Östlund</t>
+          <t>Maja Östlund, Per-Anders Blomqvist</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120026705</v>
+        <v>120026703</v>
       </c>
       <c r="B3" t="n">
-        <v>90576</v>
+        <v>90580</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1108</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>579656</v>
+        <v>579662</v>
       </c>
       <c r="R3" t="n">
-        <v>7194865</v>
+        <v>7194870</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120026702</v>
+        <v>120026701</v>
       </c>
       <c r="B4" t="n">
-        <v>90576</v>
+        <v>57320</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>579658</v>
+        <v>579689</v>
       </c>
       <c r="R4" t="n">
-        <v>7194877</v>
+        <v>7194652</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -974,17 +974,17 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Maja Östlund, Per-Anders Blomqvist</t>
+          <t>Maja Östlund, Simon Mattsson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120026703</v>
+        <v>120026705</v>
       </c>
       <c r="B5" t="n">
-        <v>90580</v>
+        <v>90576</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -997,21 +997,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1202</v>
+        <v>1108</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>579662</v>
+        <v>579656</v>
       </c>
       <c r="R5" t="n">
-        <v>7194870</v>
+        <v>7194865</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>

--- a/artfynd/A 30810-2024 artfynd.xlsx
+++ b/artfynd/A 30810-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1081,6 +1081,1144 @@
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>120461271</v>
+      </c>
+      <c r="B6" t="n">
+        <v>90598</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Luspberget, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>579771</v>
+      </c>
+      <c r="R6" t="n">
+        <v>7194839</v>
+      </c>
+      <c r="S6" t="n">
+        <v>25</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2024-10-06</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>13:31</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2024-10-06</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>13:31</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>120461276</v>
+      </c>
+      <c r="B7" t="n">
+        <v>57431</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>103031</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Lavskrika</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Perisoreus infaustus</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Luspberget, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>579809</v>
+      </c>
+      <c r="R7" t="n">
+        <v>7194765</v>
+      </c>
+      <c r="S7" t="n">
+        <v>25</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2024-10-06</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>13:20</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2024-10-06</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>13:20</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>120461274</v>
+      </c>
+      <c r="B8" t="n">
+        <v>90545</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Luspberget, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>579809</v>
+      </c>
+      <c r="R8" t="n">
+        <v>7194765</v>
+      </c>
+      <c r="S8" t="n">
+        <v>25</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2024-10-06</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>13:20</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2024-10-06</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>13:20</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>120461269</v>
+      </c>
+      <c r="B9" t="n">
+        <v>90576</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>1108</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Harticka</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Pelloporus leporinus</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Luspberget, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>579760</v>
+      </c>
+      <c r="R9" t="n">
+        <v>7194829</v>
+      </c>
+      <c r="S9" t="n">
+        <v>25</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2024-10-06</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>13:32</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2024-10-06</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>13:32</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>120461267</v>
+      </c>
+      <c r="B10" t="n">
+        <v>78542</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Luspberget, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>579664</v>
+      </c>
+      <c r="R10" t="n">
+        <v>7194660</v>
+      </c>
+      <c r="S10" t="n">
+        <v>25</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2024-10-06</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>14:29</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2024-10-06</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>14:29</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>120461273</v>
+      </c>
+      <c r="B11" t="n">
+        <v>57336</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Luspberget, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>579810</v>
+      </c>
+      <c r="R11" t="n">
+        <v>7194767</v>
+      </c>
+      <c r="S11" t="n">
+        <v>25</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2024-10-06</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>13:20</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2024-10-06</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>13:20</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>120461277</v>
+      </c>
+      <c r="B12" t="n">
+        <v>90576</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>1108</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Harticka</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Pelloporus leporinus</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Luspberget, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>579809</v>
+      </c>
+      <c r="R12" t="n">
+        <v>7194762</v>
+      </c>
+      <c r="S12" t="n">
+        <v>25</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2024-10-06</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>13:19</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2024-10-06</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>13:19</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>120461275</v>
+      </c>
+      <c r="B13" t="n">
+        <v>78542</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Luspberget, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>579809</v>
+      </c>
+      <c r="R13" t="n">
+        <v>7194765</v>
+      </c>
+      <c r="S13" t="n">
+        <v>25</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2024-10-06</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>13:20</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2024-10-06</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>13:20</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>120461268</v>
+      </c>
+      <c r="B14" t="n">
+        <v>57320</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Luspberget, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>579674</v>
+      </c>
+      <c r="R14" t="n">
+        <v>7194771</v>
+      </c>
+      <c r="S14" t="n">
+        <v>25</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2024-10-06</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>14:23</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2024-10-06</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>14:23</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>120461270</v>
+      </c>
+      <c r="B15" t="n">
+        <v>78542</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Luspberget, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>579769</v>
+      </c>
+      <c r="R15" t="n">
+        <v>7194836</v>
+      </c>
+      <c r="S15" t="n">
+        <v>25</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Vilhelmina</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2024-10-06</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>13:31</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2024-10-06</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>13:31</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 30810-2024 artfynd.xlsx
+++ b/artfynd/A 30810-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120026702</v>
+        <v>120026701</v>
       </c>
       <c r="B2" t="n">
-        <v>90576</v>
+        <v>57320</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>579658</v>
+        <v>579689</v>
       </c>
       <c r="R2" t="n">
-        <v>7194877</v>
+        <v>7194652</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -770,17 +770,17 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Maja Östlund, Per-Anders Blomqvist</t>
+          <t>Maja Östlund, Simon Mattsson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120026703</v>
+        <v>120026702</v>
       </c>
       <c r="B3" t="n">
-        <v>90580</v>
+        <v>90576</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>1108</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>579662</v>
+        <v>579658</v>
       </c>
       <c r="R3" t="n">
-        <v>7194870</v>
+        <v>7194877</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -872,17 +872,17 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Maja Östlund, Simon Mattsson</t>
+          <t>Maja Östlund, Per-Anders Blomqvist</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120026701</v>
+        <v>120026703</v>
       </c>
       <c r="B4" t="n">
-        <v>57320</v>
+        <v>90580</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>579689</v>
+        <v>579662</v>
       </c>
       <c r="R4" t="n">
-        <v>7194652</v>
+        <v>7194870</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1083,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120461271</v>
+        <v>120461274</v>
       </c>
       <c r="B6" t="n">
-        <v>90598</v>
+        <v>90545</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1095,25 +1095,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5432</v>
+        <v>5447</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>579771</v>
+        <v>579809</v>
       </c>
       <c r="R6" t="n">
-        <v>7194839</v>
+        <v>7194765</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1158,7 +1158,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1168,7 +1168,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1195,10 +1195,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120461276</v>
+        <v>120461273</v>
       </c>
       <c r="B7" t="n">
-        <v>57431</v>
+        <v>57336</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1207,20 +1207,20 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103031</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1228,9 +1228,10 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>3</t>
+      <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1239,10 +1240,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>579809</v>
+        <v>579810</v>
       </c>
       <c r="R7" t="n">
-        <v>7194765</v>
+        <v>7194767</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1311,10 +1312,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120461274</v>
+        <v>120461277</v>
       </c>
       <c r="B8" t="n">
-        <v>90545</v>
+        <v>90576</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1323,25 +1324,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5447</v>
+        <v>1108</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1354,7 +1355,7 @@
         <v>579809</v>
       </c>
       <c r="R8" t="n">
-        <v>7194765</v>
+        <v>7194762</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1386,7 +1387,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1396,7 +1397,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1423,10 +1424,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120461269</v>
+        <v>120461271</v>
       </c>
       <c r="B9" t="n">
-        <v>90576</v>
+        <v>90598</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1439,21 +1440,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1108</v>
+        <v>5432</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1463,10 +1464,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>579760</v>
+        <v>579771</v>
       </c>
       <c r="R9" t="n">
-        <v>7194829</v>
+        <v>7194839</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1498,7 +1499,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1508,7 +1509,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1535,10 +1536,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120461267</v>
+        <v>120461276</v>
       </c>
       <c r="B10" t="n">
-        <v>78542</v>
+        <v>57431</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1547,38 +1548,42 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>103031</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Luspberget, Ås lm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>579664</v>
+        <v>579809</v>
       </c>
       <c r="R10" t="n">
-        <v>7194660</v>
+        <v>7194765</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1610,7 +1615,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1620,7 +1625,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1647,10 +1652,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120461273</v>
+        <v>120461275</v>
       </c>
       <c r="B11" t="n">
-        <v>57336</v>
+        <v>78542</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1663,39 +1668,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Luspberget, Ås lm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>579810</v>
+        <v>579809</v>
       </c>
       <c r="R11" t="n">
-        <v>7194767</v>
+        <v>7194765</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1764,10 +1764,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120461277</v>
+        <v>120461268</v>
       </c>
       <c r="B12" t="n">
-        <v>90576</v>
+        <v>57320</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1780,34 +1780,43 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Luspberget, Ås lm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>579809</v>
+        <v>579674</v>
       </c>
       <c r="R12" t="n">
-        <v>7194762</v>
+        <v>7194771</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1839,7 +1848,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1849,7 +1858,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1876,7 +1885,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120461275</v>
+        <v>120461270</v>
       </c>
       <c r="B13" t="n">
         <v>78542</v>
@@ -1916,10 +1925,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>579809</v>
+        <v>579769</v>
       </c>
       <c r="R13" t="n">
-        <v>7194765</v>
+        <v>7194836</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -1951,7 +1960,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1961,7 +1970,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1988,10 +1997,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120461268</v>
+        <v>120461267</v>
       </c>
       <c r="B14" t="n">
-        <v>57320</v>
+        <v>78542</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2004,43 +2013,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Luspberget, Ås lm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>579674</v>
+        <v>579664</v>
       </c>
       <c r="R14" t="n">
-        <v>7194771</v>
+        <v>7194660</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2072,7 +2072,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2082,7 +2082,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2109,10 +2109,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120461270</v>
+        <v>120461269</v>
       </c>
       <c r="B15" t="n">
-        <v>78542</v>
+        <v>90576</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2125,21 +2125,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2149,10 +2149,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>579769</v>
+        <v>579760</v>
       </c>
       <c r="R15" t="n">
-        <v>7194836</v>
+        <v>7194829</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2184,7 +2184,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2194,7 +2194,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AD15" t="b">

--- a/artfynd/A 30810-2024 artfynd.xlsx
+++ b/artfynd/A 30810-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120026701</v>
+        <v>120026703</v>
       </c>
       <c r="B2" t="n">
-        <v>57320</v>
+        <v>90580</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>579689</v>
+        <v>579662</v>
       </c>
       <c r="R2" t="n">
-        <v>7194652</v>
+        <v>7194870</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,7 +777,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120026702</v>
+        <v>120026705</v>
       </c>
       <c r="B3" t="n">
         <v>90576</v>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>579658</v>
+        <v>579656</v>
       </c>
       <c r="R3" t="n">
-        <v>7194877</v>
+        <v>7194865</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -872,17 +872,17 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Maja Östlund, Per-Anders Blomqvist</t>
+          <t>Maja Östlund, Simon Mattsson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120026703</v>
+        <v>120026701</v>
       </c>
       <c r="B4" t="n">
-        <v>90580</v>
+        <v>57320</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>579662</v>
+        <v>579689</v>
       </c>
       <c r="R4" t="n">
-        <v>7194870</v>
+        <v>7194652</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,7 +981,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120026705</v>
+        <v>120026702</v>
       </c>
       <c r="B5" t="n">
         <v>90576</v>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>579656</v>
+        <v>579658</v>
       </c>
       <c r="R5" t="n">
-        <v>7194865</v>
+        <v>7194877</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1076,7 +1076,7 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Maja Östlund, Simon Mattsson</t>
+          <t>Maja Östlund, Per-Anders Blomqvist</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
@@ -1312,10 +1312,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120461277</v>
+        <v>120461267</v>
       </c>
       <c r="B8" t="n">
-        <v>90576</v>
+        <v>78542</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1328,21 +1328,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1352,10 +1352,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>579809</v>
+        <v>579664</v>
       </c>
       <c r="R8" t="n">
-        <v>7194762</v>
+        <v>7194660</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1387,7 +1387,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1397,7 +1397,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1424,10 +1424,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120461271</v>
+        <v>120461276</v>
       </c>
       <c r="B9" t="n">
-        <v>90598</v>
+        <v>57431</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1436,38 +1436,42 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5432</v>
+        <v>103031</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Luspberget, Ås lm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>579771</v>
+        <v>579809</v>
       </c>
       <c r="R9" t="n">
-        <v>7194839</v>
+        <v>7194765</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1499,7 +1503,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1509,7 +1513,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1536,10 +1540,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120461276</v>
+        <v>120461268</v>
       </c>
       <c r="B10" t="n">
-        <v>57431</v>
+        <v>57320</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1548,20 +1552,20 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>103031</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1571,7 +1575,12 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1580,10 +1589,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>579809</v>
+        <v>579674</v>
       </c>
       <c r="R10" t="n">
-        <v>7194765</v>
+        <v>7194771</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1615,7 +1624,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1625,7 +1634,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1652,10 +1661,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120461275</v>
+        <v>120461277</v>
       </c>
       <c r="B11" t="n">
-        <v>78542</v>
+        <v>90576</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1668,21 +1677,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1695,7 +1704,7 @@
         <v>579809</v>
       </c>
       <c r="R11" t="n">
-        <v>7194765</v>
+        <v>7194762</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1727,7 +1736,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1737,7 +1746,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1764,10 +1773,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120461268</v>
+        <v>120461271</v>
       </c>
       <c r="B12" t="n">
-        <v>57320</v>
+        <v>90598</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1780,43 +1789,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Luspberget, Ås lm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>579674</v>
+        <v>579771</v>
       </c>
       <c r="R12" t="n">
-        <v>7194771</v>
+        <v>7194839</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1848,7 +1848,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1858,7 +1858,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1885,10 +1885,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120461270</v>
+        <v>120461269</v>
       </c>
       <c r="B13" t="n">
-        <v>78542</v>
+        <v>90576</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1901,21 +1901,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1925,10 +1925,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>579769</v>
+        <v>579760</v>
       </c>
       <c r="R13" t="n">
-        <v>7194836</v>
+        <v>7194829</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -1960,7 +1960,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1970,7 +1970,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1997,7 +1997,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120461267</v>
+        <v>120461275</v>
       </c>
       <c r="B14" t="n">
         <v>78542</v>
@@ -2037,10 +2037,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>579664</v>
+        <v>579809</v>
       </c>
       <c r="R14" t="n">
-        <v>7194660</v>
+        <v>7194765</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2072,7 +2072,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2082,7 +2082,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2109,10 +2109,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120461269</v>
+        <v>120461270</v>
       </c>
       <c r="B15" t="n">
-        <v>90576</v>
+        <v>78542</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2125,21 +2125,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2149,10 +2149,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>579760</v>
+        <v>579769</v>
       </c>
       <c r="R15" t="n">
-        <v>7194829</v>
+        <v>7194836</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2184,7 +2184,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2194,7 +2194,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AD15" t="b">

--- a/artfynd/A 30810-2024 artfynd.xlsx
+++ b/artfynd/A 30810-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120026703</v>
+        <v>120026702</v>
       </c>
       <c r="B2" t="n">
-        <v>90580</v>
+        <v>90576</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1202</v>
+        <v>1108</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>579662</v>
+        <v>579658</v>
       </c>
       <c r="R2" t="n">
-        <v>7194870</v>
+        <v>7194877</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -770,17 +770,17 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Maja Östlund, Simon Mattsson</t>
+          <t>Maja Östlund, Per-Anders Blomqvist</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120026705</v>
+        <v>120026701</v>
       </c>
       <c r="B3" t="n">
-        <v>90576</v>
+        <v>57320</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>579656</v>
+        <v>579689</v>
       </c>
       <c r="R3" t="n">
-        <v>7194865</v>
+        <v>7194652</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120026701</v>
+        <v>120026703</v>
       </c>
       <c r="B4" t="n">
-        <v>57320</v>
+        <v>90580</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>579689</v>
+        <v>579662</v>
       </c>
       <c r="R4" t="n">
-        <v>7194652</v>
+        <v>7194870</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,7 +981,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120026702</v>
+        <v>120026705</v>
       </c>
       <c r="B5" t="n">
         <v>90576</v>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>579658</v>
+        <v>579656</v>
       </c>
       <c r="R5" t="n">
-        <v>7194877</v>
+        <v>7194865</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1076,17 +1076,17 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Maja Östlund, Per-Anders Blomqvist</t>
+          <t>Maja Östlund, Simon Mattsson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120461274</v>
+        <v>120461268</v>
       </c>
       <c r="B6" t="n">
-        <v>90545</v>
+        <v>57320</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1095,38 +1095,47 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Luspberget, Ås lm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>579809</v>
+        <v>579674</v>
       </c>
       <c r="R6" t="n">
-        <v>7194765</v>
+        <v>7194771</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1158,7 +1167,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1168,7 +1177,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1195,10 +1204,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120461273</v>
+        <v>120461277</v>
       </c>
       <c r="B7" t="n">
-        <v>57336</v>
+        <v>90576</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1211,39 +1220,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>1108</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Luspberget, Ås lm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>579810</v>
+        <v>579809</v>
       </c>
       <c r="R7" t="n">
-        <v>7194767</v>
+        <v>7194762</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1275,7 +1279,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1285,7 +1289,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1312,10 +1316,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120461267</v>
+        <v>120461276</v>
       </c>
       <c r="B8" t="n">
-        <v>78542</v>
+        <v>57431</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1324,38 +1328,42 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>103031</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Luspberget, Ås lm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>579664</v>
+        <v>579809</v>
       </c>
       <c r="R8" t="n">
-        <v>7194660</v>
+        <v>7194765</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1387,7 +1395,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1397,7 +1405,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1424,10 +1432,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120461276</v>
+        <v>120461269</v>
       </c>
       <c r="B9" t="n">
-        <v>57431</v>
+        <v>90576</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1436,42 +1444,38 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>103031</v>
+        <v>1108</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Luspberget, Ås lm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>579809</v>
+        <v>579760</v>
       </c>
       <c r="R9" t="n">
-        <v>7194765</v>
+        <v>7194829</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1503,7 +1507,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1513,7 +1517,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1540,10 +1544,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120461268</v>
+        <v>120461270</v>
       </c>
       <c r="B10" t="n">
-        <v>57320</v>
+        <v>78542</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1556,43 +1560,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Luspberget, Ås lm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>579674</v>
+        <v>579769</v>
       </c>
       <c r="R10" t="n">
-        <v>7194771</v>
+        <v>7194836</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1624,7 +1619,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1634,7 +1629,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1661,10 +1656,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120461277</v>
+        <v>120461274</v>
       </c>
       <c r="B11" t="n">
-        <v>90576</v>
+        <v>90545</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1673,25 +1668,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1108</v>
+        <v>5447</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1704,7 +1699,7 @@
         <v>579809</v>
       </c>
       <c r="R11" t="n">
-        <v>7194762</v>
+        <v>7194765</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1736,7 +1731,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1746,7 +1741,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1773,10 +1768,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120461271</v>
+        <v>120461267</v>
       </c>
       <c r="B12" t="n">
-        <v>90598</v>
+        <v>78542</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1789,21 +1784,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1813,10 +1808,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>579771</v>
+        <v>579664</v>
       </c>
       <c r="R12" t="n">
-        <v>7194839</v>
+        <v>7194660</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1848,7 +1843,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1858,7 +1853,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1885,10 +1880,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120461269</v>
+        <v>120461275</v>
       </c>
       <c r="B13" t="n">
-        <v>90576</v>
+        <v>78542</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1901,21 +1896,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1925,10 +1920,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>579760</v>
+        <v>579809</v>
       </c>
       <c r="R13" t="n">
-        <v>7194829</v>
+        <v>7194765</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -1960,7 +1955,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1970,7 +1965,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1997,10 +1992,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120461275</v>
+        <v>120461271</v>
       </c>
       <c r="B14" t="n">
-        <v>78542</v>
+        <v>90598</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2013,21 +2008,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2037,10 +2032,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>579809</v>
+        <v>579771</v>
       </c>
       <c r="R14" t="n">
-        <v>7194765</v>
+        <v>7194839</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2072,7 +2067,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2082,7 +2077,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2109,10 +2104,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120461270</v>
+        <v>120461273</v>
       </c>
       <c r="B15" t="n">
-        <v>78542</v>
+        <v>57336</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2125,34 +2120,39 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Luspberget, Ås lm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>579769</v>
+        <v>579810</v>
       </c>
       <c r="R15" t="n">
-        <v>7194836</v>
+        <v>7194767</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2184,7 +2184,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2194,7 +2194,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AD15" t="b">

--- a/artfynd/A 30810-2024 artfynd.xlsx
+++ b/artfynd/A 30810-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120026702</v>
+        <v>120026701</v>
       </c>
       <c r="B2" t="n">
-        <v>90576</v>
+        <v>57320</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>579658</v>
+        <v>579689</v>
       </c>
       <c r="R2" t="n">
-        <v>7194877</v>
+        <v>7194652</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -770,17 +770,17 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Maja Östlund, Per-Anders Blomqvist</t>
+          <t>Maja Östlund, Simon Mattsson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120026701</v>
+        <v>120026702</v>
       </c>
       <c r="B3" t="n">
-        <v>57320</v>
+        <v>90576</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>579689</v>
+        <v>579658</v>
       </c>
       <c r="R3" t="n">
-        <v>7194652</v>
+        <v>7194877</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -872,17 +872,17 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Maja Östlund, Simon Mattsson</t>
+          <t>Maja Östlund, Per-Anders Blomqvist</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120026703</v>
+        <v>120026705</v>
       </c>
       <c r="B4" t="n">
-        <v>90580</v>
+        <v>90576</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>1108</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>579662</v>
+        <v>579656</v>
       </c>
       <c r="R4" t="n">
-        <v>7194870</v>
+        <v>7194865</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120026705</v>
+        <v>120026703</v>
       </c>
       <c r="B5" t="n">
-        <v>90576</v>
+        <v>90580</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -997,21 +997,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1108</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>579656</v>
+        <v>579662</v>
       </c>
       <c r="R5" t="n">
-        <v>7194865</v>
+        <v>7194870</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1083,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120461268</v>
+        <v>120461269</v>
       </c>
       <c r="B6" t="n">
-        <v>57320</v>
+        <v>90576</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1099,43 +1099,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Luspberget, Ås lm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>579674</v>
+        <v>579760</v>
       </c>
       <c r="R6" t="n">
-        <v>7194771</v>
+        <v>7194829</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1167,7 +1158,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1177,7 +1168,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1204,10 +1195,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120461277</v>
+        <v>120461274</v>
       </c>
       <c r="B7" t="n">
-        <v>90576</v>
+        <v>90545</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1216,25 +1207,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1108</v>
+        <v>5447</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1247,7 +1238,7 @@
         <v>579809</v>
       </c>
       <c r="R7" t="n">
-        <v>7194762</v>
+        <v>7194765</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1279,7 +1270,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1289,7 +1280,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1316,10 +1307,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120461276</v>
+        <v>120461267</v>
       </c>
       <c r="B8" t="n">
-        <v>57431</v>
+        <v>78542</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1328,42 +1319,38 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103031</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Luspberget, Ås lm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>579809</v>
+        <v>579664</v>
       </c>
       <c r="R8" t="n">
-        <v>7194765</v>
+        <v>7194660</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1395,7 +1382,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1405,7 +1392,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1432,10 +1419,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120461269</v>
+        <v>120461276</v>
       </c>
       <c r="B9" t="n">
-        <v>90576</v>
+        <v>57431</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1444,38 +1431,42 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1108</v>
+        <v>103031</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Luspberget, Ås lm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>579760</v>
+        <v>579809</v>
       </c>
       <c r="R9" t="n">
-        <v>7194829</v>
+        <v>7194765</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1507,7 +1498,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1517,7 +1508,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1544,7 +1535,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120461270</v>
+        <v>120461275</v>
       </c>
       <c r="B10" t="n">
         <v>78542</v>
@@ -1584,10 +1575,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>579769</v>
+        <v>579809</v>
       </c>
       <c r="R10" t="n">
-        <v>7194836</v>
+        <v>7194765</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1619,7 +1610,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1629,7 +1620,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1656,10 +1647,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120461274</v>
+        <v>120461273</v>
       </c>
       <c r="B11" t="n">
-        <v>90545</v>
+        <v>57336</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1668,38 +1659,43 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5447</v>
+        <v>100049</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Luspberget, Ås lm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>579809</v>
+        <v>579810</v>
       </c>
       <c r="R11" t="n">
-        <v>7194765</v>
+        <v>7194767</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1768,10 +1764,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120461267</v>
+        <v>120461271</v>
       </c>
       <c r="B12" t="n">
-        <v>78542</v>
+        <v>90598</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1784,21 +1780,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1808,10 +1804,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>579664</v>
+        <v>579771</v>
       </c>
       <c r="R12" t="n">
-        <v>7194660</v>
+        <v>7194839</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1843,7 +1839,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1853,7 +1849,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>14:29</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1880,10 +1876,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120461275</v>
+        <v>120461277</v>
       </c>
       <c r="B13" t="n">
-        <v>78542</v>
+        <v>90576</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1896,21 +1892,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1923,7 +1919,7 @@
         <v>579809</v>
       </c>
       <c r="R13" t="n">
-        <v>7194765</v>
+        <v>7194762</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -1955,7 +1951,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1965,7 +1961,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1992,10 +1988,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120461271</v>
+        <v>120461270</v>
       </c>
       <c r="B14" t="n">
-        <v>90598</v>
+        <v>78542</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2008,21 +2004,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2032,10 +2028,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>579771</v>
+        <v>579769</v>
       </c>
       <c r="R14" t="n">
-        <v>7194839</v>
+        <v>7194836</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2104,10 +2100,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120461273</v>
+        <v>120461268</v>
       </c>
       <c r="B15" t="n">
-        <v>57336</v>
+        <v>57320</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2120,16 +2116,16 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -2137,10 +2133,14 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr"/>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -2149,10 +2149,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>579810</v>
+        <v>579674</v>
       </c>
       <c r="R15" t="n">
-        <v>7194767</v>
+        <v>7194771</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2184,7 +2184,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2194,7 +2194,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AD15" t="b">

--- a/artfynd/A 30810-2024 artfynd.xlsx
+++ b/artfynd/A 30810-2024 artfynd.xlsx
@@ -1647,10 +1647,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120461273</v>
+        <v>120461271</v>
       </c>
       <c r="B11" t="n">
-        <v>57336</v>
+        <v>90598</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1663,39 +1663,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100049</v>
+        <v>5432</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Luspberget, Ås lm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>579810</v>
+        <v>579771</v>
       </c>
       <c r="R11" t="n">
-        <v>7194767</v>
+        <v>7194839</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1727,7 +1722,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1737,7 +1732,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1764,10 +1759,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120461271</v>
+        <v>120461273</v>
       </c>
       <c r="B12" t="n">
-        <v>90598</v>
+        <v>57336</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1780,34 +1775,39 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5432</v>
+        <v>100049</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Luspberget, Ås lm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>579771</v>
+        <v>579810</v>
       </c>
       <c r="R12" t="n">
-        <v>7194839</v>
+        <v>7194767</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1839,7 +1839,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1849,7 +1849,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AD12" t="b">

--- a/artfynd/A 30810-2024 artfynd.xlsx
+++ b/artfynd/A 30810-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY15"/>
+  <dimension ref="A1:AY14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120026705</v>
+        <v>120026702</v>
       </c>
       <c r="B2" t="n">
-        <v>90576</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91905</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>579656</v>
+        <v>579658</v>
       </c>
       <c r="R2" t="n">
-        <v>7194865</v>
+        <v>7194877</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -770,22 +765,17 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Maja Östlund, Simon Mattsson</t>
+          <t>Maja Östlund, Per-Anders Blomqvist</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120026703</v>
+        <v>120026705</v>
       </c>
       <c r="B3" t="n">
-        <v>90580</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91905</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>1108</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>579662</v>
+        <v>579656</v>
       </c>
       <c r="R3" t="n">
-        <v>7194870</v>
+        <v>7194865</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,15 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120026702</v>
+        <v>120461269</v>
       </c>
       <c r="B4" t="n">
-        <v>90576</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91905</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -915,17 +900,17 @@
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Tresund, Ås lm</t>
+          <t>Luspberget, Ås lm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>579658</v>
+        <v>579760</v>
       </c>
       <c r="R4" t="n">
-        <v>7194877</v>
+        <v>7194829</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -949,12 +934,22 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-08-13</t>
+          <t>2024-10-06</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-08-13</t>
+          <t>2024-10-06</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -969,27 +964,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Maja Östlund</t>
+          <t>Isak Vahlström</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Maja Östlund, Per-Anders Blomqvist</t>
+          <t>Isak Vahlström</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120026701</v>
+        <v>120026703</v>
       </c>
       <c r="B5" t="n">
-        <v>57320</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -997,21 +987,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1011,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>579689</v>
+        <v>579662</v>
       </c>
       <c r="R5" t="n">
-        <v>7194652</v>
+        <v>7194870</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1086,16 +1076,11 @@
         <v>120461267</v>
       </c>
       <c r="B6" t="n">
-        <v>78590</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
@@ -1195,59 +1180,45 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120461268</v>
+        <v>120461270</v>
       </c>
       <c r="B7" t="n">
-        <v>57344</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Luspberget, Ås lm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>579674</v>
+        <v>579769</v>
       </c>
       <c r="R7" t="n">
-        <v>7194771</v>
+        <v>7194836</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1279,7 +1250,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1289,7 +1260,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1316,15 +1287,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120461277</v>
+        <v>120026701</v>
       </c>
       <c r="B8" t="n">
-        <v>90666</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1332,37 +1298,37 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Luspberget, Ås lm</t>
+          <t>Tresund, Ås lm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>579809</v>
+        <v>579689</v>
       </c>
       <c r="R8" t="n">
-        <v>7194762</v>
+        <v>7194652</v>
       </c>
       <c r="S8" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1386,22 +1352,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2024-10-06</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>13:19</t>
+          <t>2024-08-13</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2024-10-06</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>13:19</t>
+          <t>2024-08-13</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1416,27 +1372,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Isak Vahlström</t>
+          <t>Maja Östlund</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Isak Vahlström</t>
+          <t>Maja Östlund, Simon Mattsson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120461270</v>
+        <v>120461268</v>
       </c>
       <c r="B9" t="n">
-        <v>78590</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1444,34 +1395,43 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Luspberget, Ås lm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>579769</v>
+        <v>579674</v>
       </c>
       <c r="R9" t="n">
-        <v>7194836</v>
+        <v>7194771</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1503,7 +1463,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1513,7 +1473,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1540,15 +1500,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120461273</v>
+        <v>120461277</v>
       </c>
       <c r="B10" t="n">
-        <v>57360</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91905</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1556,39 +1511,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>1108</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Luspberget, Ås lm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>579810</v>
+        <v>579809</v>
       </c>
       <c r="R10" t="n">
-        <v>7194767</v>
+        <v>7194762</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1620,7 +1570,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1630,7 +1580,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1660,12 +1610,7 @@
         <v>120461274</v>
       </c>
       <c r="B11" t="n">
-        <v>90635</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1769,37 +1714,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120461269</v>
+        <v>120461275</v>
       </c>
       <c r="B12" t="n">
-        <v>90666</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1809,10 +1749,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>579760</v>
+        <v>579809</v>
       </c>
       <c r="R12" t="n">
-        <v>7194829</v>
+        <v>7194765</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1844,7 +1784,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1854,7 +1794,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1881,50 +1821,50 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120461275</v>
+        <v>120461273</v>
       </c>
       <c r="B13" t="n">
-        <v>78590</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Luspberget, Ås lm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>579809</v>
+        <v>579810</v>
       </c>
       <c r="R13" t="n">
-        <v>7194765</v>
+        <v>7194767</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -1993,15 +1933,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120461271</v>
+        <v>120461276</v>
       </c>
       <c r="B14" t="n">
-        <v>90688</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58057</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2009,34 +1944,38 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5432</v>
+        <v>103031</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Luspberget, Ås lm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>579771</v>
+        <v>579809</v>
       </c>
       <c r="R14" t="n">
-        <v>7194839</v>
+        <v>7194765</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2068,7 +2007,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2078,7 +2017,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2102,122 +2041,6 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
-    </row>
-    <row r="15">
-      <c r="A15" t="n">
-        <v>120461276</v>
-      </c>
-      <c r="B15" t="n">
-        <v>57455</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E15" t="n">
-        <v>103031</v>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>Lavskrika</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>Perisoreus infaustus</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="P15" t="inlineStr">
-        <is>
-          <t>Luspberget, Ås lm</t>
-        </is>
-      </c>
-      <c r="Q15" t="n">
-        <v>579809</v>
-      </c>
-      <c r="R15" t="n">
-        <v>7194765</v>
-      </c>
-      <c r="S15" t="n">
-        <v>25</v>
-      </c>
-      <c r="T15" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U15" t="inlineStr">
-        <is>
-          <t>Vilhelmina</t>
-        </is>
-      </c>
-      <c r="V15" t="inlineStr">
-        <is>
-          <t>Åsele lappmark</t>
-        </is>
-      </c>
-      <c r="W15" t="inlineStr">
-        <is>
-          <t>Vilhelmina</t>
-        </is>
-      </c>
-      <c r="Y15" t="inlineStr">
-        <is>
-          <t>2024-10-06</t>
-        </is>
-      </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>13:20</t>
-        </is>
-      </c>
-      <c r="AA15" t="inlineStr">
-        <is>
-          <t>2024-10-06</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>13:20</t>
-        </is>
-      </c>
-      <c r="AD15" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE15" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG15" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT15" t="inlineStr"/>
-      <c r="AW15" t="inlineStr">
-        <is>
-          <t>Isak Vahlström</t>
-        </is>
-      </c>
-      <c r="AX15" t="inlineStr">
-        <is>
-          <t>Isak Vahlström</t>
-        </is>
-      </c>
-      <c r="AY15" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
